--- a/FLORES DE ESTRADA/Octubre/EDESUR Octubre.xlsx
+++ b/FLORES DE ESTRADA/Octubre/EDESUR Octubre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D33A40-D7C6-4A87-B2D3-869031737DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E8CB66-FCC6-4D63-B28C-73994C39DDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,7 +233,7 @@
     <t>7-B</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 15/10</t>
+    <t>EDESUR - VENCIMIENTO 14/11</t>
   </si>
 </sst>
 </file>
@@ -334,7 +334,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +375,18 @@
       <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -610,6 +622,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -625,8 +638,14 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,13 +951,13 @@
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -951,21 +970,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="53"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1108,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="50">
-        <v>1371121.11</v>
+        <v>1458515.68</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1159,7 +1178,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>1029931.6518000003</v>
+        <v>1261015</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1189,10 +1208,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F10" s="18">
-        <v>19350</v>
-      </c>
-      <c r="G10" s="58">
         <v>19700.2</v>
+      </c>
+      <c r="G10" s="51">
+        <v>19937.5</v>
       </c>
       <c r="H10" s="19">
         <v>0</v>
@@ -1203,31 +1222,31 @@
       </c>
       <c r="J10" s="20">
         <f>(G10-F10)*93.78</f>
-        <v>32841.756000000067</v>
+        <v>22253.993999999933</v>
       </c>
       <c r="K10" s="21">
         <f>G10-F10</f>
-        <v>350.20000000000073</v>
+        <v>237.29999999999927</v>
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>50466.650938200022</v>
+        <v>61789.735000000001</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>83311.406938200089</v>
+        <v>84046.728999999934</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
-        <v>42.077842408712449</v>
+        <v>28.512484304932649</v>
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>3.1887315961795024</v>
+        <v>1.7647683810263901</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>2488.8050108181014</v>
+        <v>1377.4017213910975</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1241,47 +1260,47 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="36">
         <v>2</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="36">
         <v>3.89</v>
       </c>
-      <c r="F11" s="39">
-        <v>17143.900000000001</v>
-      </c>
-      <c r="G11" s="58">
+      <c r="F11" s="36">
+        <v>17213.900000000001</v>
+      </c>
+      <c r="G11" s="66">
         <f>F11+70</f>
-        <v>17213.900000000001</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0</v>
-      </c>
-      <c r="I11" s="41">
+        <v>17283.900000000001</v>
+      </c>
+      <c r="H11" s="37">
+        <v>0</v>
+      </c>
+      <c r="I11" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="38">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="65">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="37">
         <f>L9*E11/100</f>
-        <v>40064.341255020016</v>
-      </c>
-      <c r="M11" s="40">
+        <v>49053.483500000002</v>
+      </c>
+      <c r="M11" s="37">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>46629.941255020014</v>
+        <v>55619.083500000001</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1321,11 +1340,11 @@
         <v>4</v>
       </c>
       <c r="F12" s="39">
-        <v>11586.3</v>
-      </c>
-      <c r="G12" s="58">
+        <v>11671.3</v>
+      </c>
+      <c r="G12" s="51">
         <f>F12+85</f>
-        <v>11671.3</v>
+        <v>11756.3</v>
       </c>
       <c r="H12" s="40">
         <v>0</v>
@@ -1344,11 +1363,11 @@
       </c>
       <c r="L12" s="40">
         <f>L9*E12/100</f>
-        <v>41197.266072000013</v>
+        <v>50440.6</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="3"/>
-        <v>49169.566072000016</v>
+        <v>58412.9</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1356,11 +1375,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>0.77396397965521757</v>
+        <v>0.6321336383786077</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>604.07888612089732</v>
+        <v>493.3803047545033</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1380,10 +1399,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="39">
-        <v>29144.799999999999</v>
-      </c>
-      <c r="G13" s="58">
         <v>29605.7</v>
+      </c>
+      <c r="G13" s="51">
+        <v>29923.5</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
@@ -1394,19 +1413,19 @@
       </c>
       <c r="J13" s="41">
         <f t="shared" si="5"/>
-        <v>43223.202000000136</v>
+        <v>29803.283999999931</v>
       </c>
       <c r="K13" s="42">
         <f t="shared" si="2"/>
-        <v>460.90000000000146</v>
+        <v>317.79999999999927</v>
       </c>
       <c r="L13" s="40">
         <f>L9*E13/100</f>
-        <v>50466.650938200022</v>
+        <v>61789.735000000001</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="3"/>
-        <v>93690.852938200158</v>
+        <v>91594.018999999927</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1414,11 +1433,11 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>4.1967058614481276</v>
+        <v>2.3634361209026009</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>3275.5289248602635</v>
+        <v>1844.6618923644801</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1438,10 +1457,10 @@
         <v>3.89</v>
       </c>
       <c r="F14" s="39">
-        <v>6798</v>
-      </c>
-      <c r="G14" s="58">
         <v>7104.9</v>
+      </c>
+      <c r="G14" s="51">
+        <v>7341.7</v>
       </c>
       <c r="H14" s="26">
         <v>0</v>
@@ -1452,19 +1471,19 @@
       </c>
       <c r="J14" s="41">
         <f t="shared" si="5"/>
-        <v>28781.081999999966</v>
+        <v>22207.104000000018</v>
       </c>
       <c r="K14" s="42">
         <f t="shared" si="2"/>
-        <v>306.89999999999964</v>
+        <v>236.80000000000018</v>
       </c>
       <c r="L14" s="40">
         <f>L9*E14/100</f>
-        <v>40064.341255020016</v>
+        <v>49053.483500000002</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="3"/>
-        <v>68846.423255019981</v>
+        <v>71261.587500000023</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1472,11 +1491,11 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>2.7944652394845408</v>
+        <v>1.7610499478594637</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>2181.0801194176838</v>
+        <v>1374.4994843043114</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
@@ -1499,11 +1518,11 @@
         <v>4</v>
       </c>
       <c r="F15" s="39">
-        <v>13896.7</v>
-      </c>
-      <c r="G15" s="58">
+        <v>14166.7</v>
+      </c>
+      <c r="G15" s="51">
         <f>F15+270</f>
-        <v>14166.7</v>
+        <v>14436.7</v>
       </c>
       <c r="H15" s="40">
         <v>0</v>
@@ -1522,11 +1541,11 @@
       </c>
       <c r="L15" s="40">
         <f>L9*E15/100</f>
-        <v>41197.266072000013</v>
+        <v>50440.6</v>
       </c>
       <c r="M15" s="40">
         <f t="shared" si="3"/>
-        <v>66518.866072000004</v>
+        <v>75762.2</v>
       </c>
       <c r="N15" s="46" t="e">
         <f t="shared" si="4"/>
@@ -1534,11 +1553,11 @@
       </c>
       <c r="O15" s="47">
         <f>J15/L9*100</f>
-        <v>2.4584738177283376</v>
+        <v>2.0079539101438124</v>
       </c>
       <c r="P15" s="41">
         <f>C7*O15/100</f>
-        <v>1918.8388147369676</v>
+        <v>1567.2080268672455</v>
       </c>
       <c r="Y15" s="49"/>
     </row>
@@ -1559,9 +1578,9 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>19390</v>
-      </c>
-      <c r="G16" s="58">
+        <v>19618.5</v>
+      </c>
+      <c r="G16" s="59">
         <v>19618.5</v>
       </c>
       <c r="H16" s="19">
@@ -1573,19 +1592,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>21428.73</v>
+        <v>0</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>228.5</v>
+        <v>0</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>50466.650938200022</v>
+        <v>61789.735000000001</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>71896.380938200018</v>
+        <v>61790.735000000001</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1593,11 +1612,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>2.0805972864849078</v>
+        <v>0</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>1623.9061821014704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1617,9 +1636,9 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>6352.68</v>
-      </c>
-      <c r="G17" s="58">
+        <v>6990.37</v>
+      </c>
+      <c r="G17" s="59">
         <v>6990.37</v>
       </c>
       <c r="H17" s="26">
@@ -1631,19 +1650,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>59802.568199999965</v>
+        <v>0</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>637.6899999999996</v>
+        <v>0</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>40064.341255020016</v>
+        <v>49053.483500000002</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>99867.909455019981</v>
+        <v>49054.483500000002</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1651,11 +1670,11 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>5.8064598845451219</v>
+        <v>0</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>4531.9419398874679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1675,9 +1694,9 @@
         <v>4</v>
       </c>
       <c r="F18" s="39">
-        <v>21581.4</v>
-      </c>
-      <c r="G18" s="58">
+        <v>21845.1</v>
+      </c>
+      <c r="G18" s="59">
         <v>21845.1</v>
       </c>
       <c r="H18" s="45">
@@ -1689,19 +1708,19 @@
       </c>
       <c r="J18" s="41">
         <f t="shared" si="5"/>
-        <v>24729.785999999727</v>
+        <v>0</v>
       </c>
       <c r="K18" s="42">
         <f t="shared" si="2"/>
-        <v>263.69999999999709</v>
+        <v>0</v>
       </c>
       <c r="L18" s="40">
         <f>L9*E18/100</f>
-        <v>41197.266072000013</v>
+        <v>50440.6</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="3"/>
-        <v>65928.052071999744</v>
+        <v>50441.599999999999</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1709,11 +1728,11 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>2.4011094286479837</v>
+        <v>0</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>1874.0659090597514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1733,10 +1752,10 @@
         <v>12.66</v>
       </c>
       <c r="F19" s="39">
-        <v>23741.3</v>
-      </c>
-      <c r="G19" s="58">
         <v>23882.6</v>
+      </c>
+      <c r="G19" s="51">
+        <v>24065</v>
       </c>
       <c r="H19" s="40">
         <v>0</v>
@@ -1747,19 +1766,19 @@
       </c>
       <c r="J19" s="41">
         <f t="shared" si="5"/>
-        <v>13251.113999999932</v>
+        <v>17105.472000000136</v>
       </c>
       <c r="K19" s="42">
         <f t="shared" si="2"/>
-        <v>141.29999999999927</v>
+        <v>182.40000000000146</v>
       </c>
       <c r="L19" s="40">
         <f>L9*E19/100</f>
-        <v>130389.34711788004</v>
+        <v>159644.49900000001</v>
       </c>
       <c r="M19" s="40">
         <f>J19+L19+1</f>
-        <v>143641.46111787998</v>
+        <v>176750.97100000014</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1767,11 +1786,11 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>1.2866012979444903</v>
+        <v>1.3564844192971643</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>1004.1923130456747</v>
+        <v>1058.7360892614367</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1791,11 +1810,11 @@
         <v>7.75</v>
       </c>
       <c r="F20" s="39">
-        <v>18345.099999999999</v>
-      </c>
-      <c r="G20" s="58">
+        <v>18545.099999999999</v>
+      </c>
+      <c r="G20" s="51">
         <f>F20+200</f>
-        <v>18545.099999999999</v>
+        <v>18745.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -1814,11 +1833,11 @@
       </c>
       <c r="L20" s="40">
         <f>L9*E20/100</f>
-        <v>79819.703014500032</v>
+        <v>97728.662500000006</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="3"/>
-        <v>98576.703014500032</v>
+        <v>116485.66250000001</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1826,57 +1845,57 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>1.8210917168358056</v>
+        <v>1.4873732667731947</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>1421.3620849903464</v>
+        <v>1160.8948347164785</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>12</v>
       </c>
-      <c r="B21" s="39">
+      <c r="B21" s="36">
         <v>12</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="36">
         <v>7.51</v>
       </c>
-      <c r="F21" s="39">
-        <v>15188.8</v>
-      </c>
-      <c r="G21" s="58">
+      <c r="F21" s="36">
         <v>15233</v>
       </c>
-      <c r="H21" s="26">
-        <v>0</v>
-      </c>
-      <c r="I21" s="41">
+      <c r="G21" s="66">
+        <v>15269.3</v>
+      </c>
+      <c r="H21" s="64">
+        <v>0</v>
+      </c>
+      <c r="I21" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="38">
         <f t="shared" si="5"/>
-        <v>4145.0760000000682</v>
-      </c>
-      <c r="K21" s="42">
+        <v>3404.2139999999317</v>
+      </c>
+      <c r="K21" s="65">
         <f t="shared" si="2"/>
-        <v>44.200000000000728</v>
-      </c>
-      <c r="L21" s="40">
+        <v>36.299999999999272</v>
+      </c>
+      <c r="L21" s="37">
         <f>L9*E21/100</f>
-        <v>77347.867050180022</v>
-      </c>
-      <c r="M21" s="40">
+        <v>94702.226500000004</v>
+      </c>
+      <c r="M21" s="37">
         <f t="shared" si="3"/>
-        <v>81493.943050180096</v>
+        <v>98107.440499999939</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1884,62 +1903,62 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>0.40246126942071975</v>
+        <v>0.26995824791932943</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>314.12102078287177</v>
+        <v>210.70241250103663</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
-        <v>44.200000000000728</v>
+        <v>36.299999999999272</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>13</v>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="36">
         <v>13</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="36">
         <v>4.45</v>
       </c>
-      <c r="F22" s="39">
-        <v>11414.2</v>
-      </c>
-      <c r="G22" s="58">
+      <c r="F22" s="36">
+        <v>11607.2</v>
+      </c>
+      <c r="G22" s="66">
         <f>F22+193</f>
-        <v>11607.2</v>
-      </c>
-      <c r="H22" s="26">
-        <v>0</v>
-      </c>
-      <c r="I22" s="41">
+        <v>11800.2</v>
+      </c>
+      <c r="H22" s="64">
+        <v>0</v>
+      </c>
+      <c r="I22" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="38">
         <f t="shared" si="5"/>
         <v>18099.54</v>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="65">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="37">
         <f>L9*E22/100</f>
-        <v>45831.958505100018</v>
-      </c>
-      <c r="M22" s="40">
+        <v>56115.167500000003</v>
+      </c>
+      <c r="M22" s="37">
         <f t="shared" si="3"/>
-        <v>63932.498505100019</v>
+        <v>74215.707500000004</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1947,11 +1966,11 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>1.7573535067465527</v>
+        <v>1.4353152024361329</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>1371.6144120156844</v>
+        <v>1120.2635155014018</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
@@ -1977,8 +1996,7 @@
       <c r="F23" s="39">
         <v>20525.400000000001</v>
       </c>
-      <c r="G23" s="58">
-        <f>F23</f>
+      <c r="G23" s="51">
         <v>20525.400000000001</v>
       </c>
       <c r="H23" s="40">
@@ -1998,11 +2016,11 @@
       </c>
       <c r="L23" s="40">
         <f>L9*E23/100</f>
-        <v>63546.782916060023</v>
+        <v>77804.625499999995</v>
       </c>
       <c r="M23" s="40">
         <f>J23+L23+1</f>
-        <v>63547.782916060023</v>
+        <v>77805.625499999995</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2034,10 +2052,10 @@
         <v>4.45</v>
       </c>
       <c r="F24" s="39">
-        <v>30932.2</v>
-      </c>
-      <c r="G24" s="58">
         <v>31147.8</v>
+      </c>
+      <c r="G24" s="51">
+        <v>31291.8</v>
       </c>
       <c r="H24" s="40">
         <v>0</v>
@@ -2048,19 +2066,19 @@
       </c>
       <c r="J24" s="41">
         <f t="shared" si="5"/>
-        <v>20218.967999999863</v>
+        <v>13504.32</v>
       </c>
       <c r="K24" s="42">
         <f t="shared" si="2"/>
-        <v>215.59999999999854</v>
+        <v>144</v>
       </c>
       <c r="L24" s="40">
         <f>L9*E24/100</f>
-        <v>45831.958505100018</v>
+        <v>56115.167500000003</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="3"/>
-        <v>66051.92650509988</v>
+        <v>69620.487500000003</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2068,11 +2086,11 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>1.9631368707489854</v>
+        <v>1.0709087520767002</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>1532.2283276195831</v>
+        <v>835.84428099586455</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2092,10 +2110,10 @@
         <v>9.19</v>
       </c>
       <c r="F25" s="39">
-        <v>11746.3</v>
-      </c>
-      <c r="G25" s="58">
         <v>11917.5</v>
+      </c>
+      <c r="G25" s="51">
+        <v>12050.9</v>
       </c>
       <c r="H25" s="40">
         <v>0</v>
@@ -2106,19 +2124,19 @@
       </c>
       <c r="J25" s="41">
         <f t="shared" si="5"/>
-        <v>16055.136000000068</v>
+        <v>12510.251999999966</v>
       </c>
       <c r="K25" s="42">
         <f t="shared" si="2"/>
-        <v>171.20000000000073</v>
+        <v>133.39999999999964</v>
       </c>
       <c r="L25" s="40">
         <f>L9*E25/100</f>
-        <v>94650.718800420029</v>
+        <v>115887.2785</v>
       </c>
       <c r="M25" s="40">
         <f>J25+L25+1</f>
-        <v>110706.8548004201</v>
+        <v>128398.53049999996</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2126,11 +2144,11 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>1.5588545096114563</v>
+        <v>0.99207796893771816</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>1216.6859447517415</v>
+        <v>774.31685475588904</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2169,11 +2187,11 @@
       <c r="K26" s="40"/>
       <c r="L26" s="40">
         <f>L9*E26/100</f>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2192,43 +2210,43 @@
       <c r="A27" s="18">
         <v>18</v>
       </c>
-      <c r="B27" s="36">
+      <c r="B27" s="60">
         <v>18</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="60">
         <v>1.18</v>
       </c>
-      <c r="F27" s="36">
-        <v>0</v>
-      </c>
-      <c r="G27" s="36">
-        <v>0</v>
-      </c>
-      <c r="H27" s="37">
-        <v>0</v>
-      </c>
-      <c r="I27" s="38">
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60">
+        <v>0</v>
+      </c>
+      <c r="H27" s="61">
+        <v>0</v>
+      </c>
+      <c r="I27" s="62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="62">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37">
+      <c r="K27" s="61"/>
+      <c r="L27" s="61">
         <f>L26</f>
-        <v>12153.193491240005</v>
-      </c>
-      <c r="M27" s="37">
+        <v>14879.976999999999</v>
+      </c>
+      <c r="M27" s="61">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2247,43 +2265,43 @@
       <c r="A28" s="18">
         <v>19</v>
       </c>
-      <c r="B28" s="36">
+      <c r="B28" s="60">
         <v>19</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="60">
         <v>1.18</v>
       </c>
-      <c r="F28" s="36">
-        <v>0</v>
-      </c>
-      <c r="G28" s="36">
-        <v>0</v>
-      </c>
-      <c r="H28" s="37">
-        <v>0</v>
-      </c>
-      <c r="I28" s="38">
+      <c r="F28" s="60">
+        <v>0</v>
+      </c>
+      <c r="G28" s="60">
+        <v>0</v>
+      </c>
+      <c r="H28" s="61">
+        <v>0</v>
+      </c>
+      <c r="I28" s="62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="62">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37">
+      <c r="K28" s="61"/>
+      <c r="L28" s="61">
         <f>L27</f>
-        <v>12153.193491240005</v>
-      </c>
-      <c r="M28" s="37">
+        <v>14879.976999999999</v>
+      </c>
+      <c r="M28" s="61">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2334,11 +2352,11 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40">
         <f>L28</f>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2389,11 +2407,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2444,11 +2462,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2499,11 +2517,11 @@
       <c r="K32" s="40"/>
       <c r="L32" s="40">
         <f t="shared" si="7"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="M32" s="40">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2519,46 +2537,46 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="39">
+      <c r="A33" s="36">
         <v>24</v>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="36">
         <v>24</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="36">
         <v>1.18</v>
       </c>
-      <c r="F33" s="39">
-        <v>0</v>
-      </c>
-      <c r="G33" s="39">
-        <v>0</v>
-      </c>
-      <c r="H33" s="40">
-        <v>0</v>
-      </c>
-      <c r="I33" s="41">
+      <c r="F33" s="36">
+        <v>0</v>
+      </c>
+      <c r="G33" s="36">
+        <v>0</v>
+      </c>
+      <c r="H33" s="37">
+        <v>0</v>
+      </c>
+      <c r="I33" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40">
+      <c r="K33" s="37"/>
+      <c r="L33" s="37">
         <f t="shared" si="7"/>
-        <v>12153.193491240005</v>
-      </c>
-      <c r="M33" s="40">
+        <v>14879.976999999999</v>
+      </c>
+      <c r="M33" s="37">
         <f t="shared" si="6"/>
-        <v>12153.193491240005</v>
+        <v>14879.976999999999</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2590,19 +2608,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>341189.45819999982</v>
+        <v>197500.67999999993</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>3638.1899999999978</v>
+        <v>2105.9999999999991</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>1029828.6586348205</v>
+        <v>1260888.8984999994</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>1371036.1168348205</v>
+        <v>1458407.5784999996</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2614,19 +2632,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="55"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="56"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2644,86 +2662,86 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>1371018.1168348202</v>
+        <v>1458389.5784999994</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="57"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="58"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6595,21 +6613,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="53"/>
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8201,19 +8219,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="55"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="56"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>

--- a/FLORES DE ESTRADA/Octubre/EDESUR Octubre.xlsx
+++ b/FLORES DE ESTRADA/Octubre/EDESUR Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E8CB66-FCC6-4D63-B28C-73994C39DDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B974069-F499-46CE-87F6-B5E44CB6B705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,7 +622,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -638,14 +644,8 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,14 +950,14 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -970,21 +970,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>1261015</v>
+        <v>1215906.8199999996</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1230,11 +1230,11 @@
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>61789.735000000001</v>
+        <v>59579.434179999989</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>84046.728999999934</v>
+        <v>81836.42817999993</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
@@ -1242,11 +1242,11 @@
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>1.7647683810263901</v>
+        <v>1.8302384388303654</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>1377.4017213910975</v>
+        <v>1428.5011015071002</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1275,7 +1275,7 @@
       <c r="F11" s="36">
         <v>17213.900000000001</v>
       </c>
-      <c r="G11" s="66">
+      <c r="G11" s="65">
         <f>F11+70</f>
         <v>17283.900000000001</v>
       </c>
@@ -1290,17 +1290,17 @@
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="65">
+      <c r="K11" s="57">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
       <c r="L11" s="37">
         <f>L9*E11/100</f>
-        <v>49053.483500000002</v>
+        <v>47298.775297999986</v>
       </c>
       <c r="M11" s="37">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>55619.083500000001</v>
+        <v>53864.375297999984</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="L12" s="40">
         <f>L9*E12/100</f>
-        <v>50440.6</v>
+        <v>48636.272799999984</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="3"/>
-        <v>58412.9</v>
+        <v>56608.572799999987</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1375,11 +1375,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>0.6321336383786077</v>
+        <v>0.65558477581366004</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>493.3803047545033</v>
+        <v>511.68391752256167</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1421,11 +1421,11 @@
       </c>
       <c r="L13" s="40">
         <f>L9*E13/100</f>
-        <v>61789.735000000001</v>
+        <v>59579.434179999989</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="3"/>
-        <v>91594.018999999927</v>
+        <v>89383.718179999923</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>2.3634361209026009</v>
+        <v>2.4511157853362433</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>1844.6618923644801</v>
+        <v>1913.095870454938</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="L14" s="40">
         <f>L9*E14/100</f>
-        <v>49053.483500000002</v>
+        <v>47298.775297999986</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="3"/>
-        <v>71261.587500000023</v>
+        <v>69506.879298</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>1.7610499478594637</v>
+        <v>1.8263820577961745</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>1374.4994843043114</v>
+        <v>1425.4911961099142</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
@@ -1541,11 +1541,11 @@
       </c>
       <c r="L15" s="40">
         <f>L9*E15/100</f>
-        <v>50440.6</v>
+        <v>48636.272799999984</v>
       </c>
       <c r="M15" s="40">
         <f t="shared" si="3"/>
-        <v>75762.2</v>
+        <v>73957.872799999983</v>
       </c>
       <c r="N15" s="46" t="e">
         <f t="shared" si="4"/>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="O15" s="47">
         <f>J15/L9*100</f>
-        <v>2.0079539101438124</v>
+        <v>2.0824457584669198</v>
       </c>
       <c r="P15" s="41">
         <f>C7*O15/100</f>
-        <v>1567.2080268672455</v>
+        <v>1625.3489144834309</v>
       </c>
       <c r="Y15" s="49"/>
     </row>
@@ -1580,8 +1580,8 @@
       <c r="F16" s="18">
         <v>19618.5</v>
       </c>
-      <c r="G16" s="59">
-        <v>19618.5</v>
+      <c r="G16" s="51">
+        <v>19858.7</v>
       </c>
       <c r="H16" s="19">
         <v>0</v>
@@ -1592,19 +1592,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>22525.956000000067</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240.20000000000073</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>61789.735000000001</v>
+        <v>59579.434179999989</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>61790.735000000001</v>
+        <v>82106.39018000006</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>0</v>
+        <v>1.8526054488287247</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>0</v>
+        <v>1445.9585528108196</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1636,10 +1636,11 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>6990.37</v>
-      </c>
-      <c r="G17" s="59">
-        <v>6990.37</v>
+        <v>6631.43</v>
+      </c>
+      <c r="G17" s="51">
+        <f>F17+15</f>
+        <v>6646.43</v>
       </c>
       <c r="H17" s="26">
         <v>0</v>
@@ -1650,19 +1651,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1406.7</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>49053.483500000002</v>
+        <v>47298.775297999986</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>49054.483500000002</v>
+        <v>48706.475297999983</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1670,11 +1671,11 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>0</v>
+        <v>0.11569143102594</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>0</v>
+        <v>90.297161915746159</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1696,8 +1697,8 @@
       <c r="F18" s="39">
         <v>21845.1</v>
       </c>
-      <c r="G18" s="59">
-        <v>21845.1</v>
+      <c r="G18" s="51">
+        <v>22070.9</v>
       </c>
       <c r="H18" s="45">
         <v>0</v>
@@ -1708,19 +1709,19 @@
       </c>
       <c r="J18" s="41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>21175.524000000274</v>
       </c>
       <c r="K18" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>225.80000000000291</v>
       </c>
       <c r="L18" s="40">
         <f>L9*E18/100</f>
-        <v>50440.6</v>
+        <v>48636.272799999984</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="3"/>
-        <v>50441.599999999999</v>
+        <v>69812.796800000258</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1728,11 +1729,11 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>0</v>
+        <v>1.7415416750438395</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>0</v>
+        <v>1359.2732773717166</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1774,11 +1775,11 @@
       </c>
       <c r="L19" s="40">
         <f>L9*E19/100</f>
-        <v>159644.49900000001</v>
+        <v>153933.80341199995</v>
       </c>
       <c r="M19" s="40">
         <f>J19+L19+1</f>
-        <v>176750.97100000014</v>
+        <v>171040.27541200008</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1786,11 +1787,11 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>1.3564844192971643</v>
+        <v>1.4068078012754417</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>1058.7360892614367</v>
+        <v>1098.0134888954824</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1833,11 +1834,11 @@
       </c>
       <c r="L20" s="40">
         <f>L9*E20/100</f>
-        <v>97728.662500000006</v>
+        <v>94232.778549999974</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="3"/>
-        <v>116485.66250000001</v>
+        <v>112989.77854999997</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1845,11 +1846,11 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>1.4873732667731947</v>
+        <v>1.5425524136792002</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>1160.8948347164785</v>
+        <v>1203.9621588766158</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1862,7 +1863,7 @@
       <c r="C21" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="55" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="36">
@@ -1871,10 +1872,10 @@
       <c r="F21" s="36">
         <v>15233</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="65">
         <v>15269.3</v>
       </c>
-      <c r="H21" s="64">
+      <c r="H21" s="56">
         <v>0</v>
       </c>
       <c r="I21" s="38">
@@ -1885,17 +1886,17 @@
         <f t="shared" si="5"/>
         <v>3404.2139999999317</v>
       </c>
-      <c r="K21" s="65">
+      <c r="K21" s="57">
         <f t="shared" si="2"/>
         <v>36.299999999999272</v>
       </c>
       <c r="L21" s="37">
         <f>L9*E21/100</f>
-        <v>94702.226500000004</v>
+        <v>91314.602181999959</v>
       </c>
       <c r="M21" s="37">
         <f t="shared" si="3"/>
-        <v>98107.440499999939</v>
+        <v>94719.816181999893</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1903,11 +1904,11 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>0.26995824791932943</v>
+        <v>0.27997326308276921</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>210.70241250103663</v>
+        <v>218.51913183610137</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
@@ -1933,11 +1934,11 @@
       <c r="F22" s="36">
         <v>11607.2</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="65">
         <f>F22+193</f>
         <v>11800.2</v>
       </c>
-      <c r="H22" s="64">
+      <c r="H22" s="56">
         <v>0</v>
       </c>
       <c r="I22" s="38">
@@ -1948,17 +1949,17 @@
         <f t="shared" si="5"/>
         <v>18099.54</v>
       </c>
-      <c r="K22" s="65">
+      <c r="K22" s="57">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
       <c r="L22" s="37">
         <f>L9*E22/100</f>
-        <v>56115.167500000003</v>
+        <v>54107.853489999987</v>
       </c>
       <c r="M22" s="37">
         <f t="shared" si="3"/>
-        <v>74215.707500000004</v>
+        <v>72208.393489999988</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1966,11 +1967,11 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>1.4353152024361329</v>
+        <v>1.4885630792004281</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>1120.2635155014018</v>
+        <v>1161.823483315934</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
@@ -2016,11 +2017,11 @@
       </c>
       <c r="L23" s="40">
         <f>L9*E23/100</f>
-        <v>77804.625499999995</v>
+        <v>75021.450793999975</v>
       </c>
       <c r="M23" s="40">
         <f>J23+L23+1</f>
-        <v>77805.625499999995</v>
+        <v>75022.450793999975</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2074,11 +2075,11 @@
       </c>
       <c r="L24" s="40">
         <f>L9*E24/100</f>
-        <v>56115.167500000003</v>
+        <v>54107.853489999987</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="3"/>
-        <v>69620.487500000003</v>
+        <v>67613.173489999986</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2086,11 +2087,11 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>1.0709087520767002</v>
+        <v>1.110637737849024</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>835.84428099586455</v>
+        <v>866.85275439116322</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2132,11 +2133,11 @@
       </c>
       <c r="L25" s="40">
         <f>L9*E25/100</f>
-        <v>115887.2785</v>
+        <v>111741.83675799996</v>
       </c>
       <c r="M25" s="40">
         <f>J25+L25+1</f>
-        <v>128398.53049999996</v>
+        <v>124253.08875799993</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2144,11 +2145,11 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>0.99207796893771816</v>
+        <v>1.0288824599240236</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>774.31685475588904</v>
+        <v>803.04275997070044</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2170,7 +2171,7 @@
       <c r="F26" s="39">
         <v>0</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="51">
         <v>0</v>
       </c>
       <c r="H26" s="40">
@@ -2187,11 +2188,11 @@
       <c r="K26" s="40"/>
       <c r="L26" s="40">
         <f>L9*E26/100</f>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2210,43 +2211,43 @@
       <c r="A27" s="18">
         <v>18</v>
       </c>
-      <c r="B27" s="60">
+      <c r="B27" s="52">
         <v>18</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="60" t="s">
+      <c r="D27" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="60">
+      <c r="E27" s="52">
         <v>1.18</v>
       </c>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60">
-        <v>0</v>
-      </c>
-      <c r="H27" s="61">
-        <v>0</v>
-      </c>
-      <c r="I27" s="62">
+      <c r="F27" s="52">
+        <v>0</v>
+      </c>
+      <c r="G27" s="66">
+        <v>0</v>
+      </c>
+      <c r="H27" s="53">
+        <v>0</v>
+      </c>
+      <c r="I27" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="62">
+      <c r="J27" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61">
+      <c r="K27" s="53"/>
+      <c r="L27" s="53">
         <f>L26</f>
-        <v>14879.976999999999</v>
-      </c>
-      <c r="M27" s="61">
+        <v>14347.700475999995</v>
+      </c>
+      <c r="M27" s="53">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2265,43 +2266,43 @@
       <c r="A28" s="18">
         <v>19</v>
       </c>
-      <c r="B28" s="60">
+      <c r="B28" s="52">
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="60" t="s">
+      <c r="D28" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="60">
+      <c r="E28" s="52">
         <v>1.18</v>
       </c>
-      <c r="F28" s="60">
-        <v>0</v>
-      </c>
-      <c r="G28" s="60">
-        <v>0</v>
-      </c>
-      <c r="H28" s="61">
-        <v>0</v>
-      </c>
-      <c r="I28" s="62">
+      <c r="F28" s="52">
+        <v>0</v>
+      </c>
+      <c r="G28" s="66">
+        <v>0</v>
+      </c>
+      <c r="H28" s="53">
+        <v>0</v>
+      </c>
+      <c r="I28" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="62">
+      <c r="J28" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61">
+      <c r="K28" s="53"/>
+      <c r="L28" s="53">
         <f>L27</f>
-        <v>14879.976999999999</v>
-      </c>
-      <c r="M28" s="61">
+        <v>14347.700475999995</v>
+      </c>
+      <c r="M28" s="53">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2352,11 +2353,11 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40">
         <f>L28</f>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2407,11 +2408,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2462,11 +2463,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2517,11 +2518,11 @@
       <c r="K32" s="40"/>
       <c r="L32" s="40">
         <f t="shared" si="7"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M32" s="40">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2546,7 +2547,7 @@
       <c r="C33" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="55" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="36">
@@ -2572,11 +2573,11 @@
       <c r="K33" s="37"/>
       <c r="L33" s="37">
         <f t="shared" si="7"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="6"/>
-        <v>14879.976999999999</v>
+        <v>14347.700475999995</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2608,19 +2609,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>197500.67999999993</v>
+        <v>242608.86000000028</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>2105.9999999999991</v>
+        <v>2587.0000000000027</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>1260888.8984999994</v>
+        <v>1215785.2293180004</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>1458407.5784999996</v>
+        <v>1458412.0893180005</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2632,19 +2633,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="56"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
+      <c r="M35" s="62"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2662,86 +2663,86 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>1458389.5784999994</v>
+        <v>1458394.0893180007</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="58"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="64"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="58"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="64"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6613,21 +6614,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="54"/>
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8219,19 +8220,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="56"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
+      <c r="M35" s="62"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
